--- a/tests/fixtures/source/FX-004-warning-cells.xlsx
+++ b/tests/fixtures/source/FX-004-warning-cells.xlsx
@@ -442,6 +442,7 @@
         <v>0.4</v>
       </c>
       <c r="C4">
+        <f>0.2+0.3</f>
         <v>0.5</v>
       </c>
     </row>

--- a/tests/fixtures/source/FX-004-warning-cells.xlsx
+++ b/tests/fixtures/source/FX-004-warning-cells.xlsx
@@ -403,13 +403,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v/>
+        <v>Synthetic Sample A</v>
       </c>
       <c r="B1" t="str">
         <v>Merged Synthetic Sample</v>
       </c>
       <c r="C1" t="str">
-        <v>Synthetic Sample C</v>
+        <v/>
       </c>
     </row>
     <row r="2">
